--- a/site/Dynamics-365-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dynamics-365-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,51 +947,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Creation Email Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01M3KRCR0Q6W9WCAMWWDSNAGG3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01M3KRCR0Q6W9WCAMWWDSNAGG3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Deactivation Email Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01M3KRVFJ0CNKR3NE4A4XREQNB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01M3KRVFJ0CNKR3NE4A4XREQNB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EntraID to D365 Employees</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Entra Users to D365 Users</t>
+          <t>Developer Mode</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01M3KSXBS72MWFJJ3ERKXR21NM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01M3KSXBS72MWFJJ3ERKXR21NM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,76 +1089,142 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>EntraID to D365 Employees</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Entra Users to D365 Users</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dynamics-365-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dynamics-365-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,51 +1057,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Developer Mode</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M3KSXBS72MWFJJ3ERKXR21NM</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01M3KSXBS72MWFJJ3ERKXR21NM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>EntraID to D365 Employees</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EntraID to D365 Employees</t>
+          <t>Entra Users to D365 Users</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,41 +1111,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Entra Users to D365 Users</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,41 +1155,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,32 +1199,10 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics-365-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
